--- a/event_planner_forms/013_holiday_booth_request_form--event_planner_forms.xlsx
+++ b/event_planner_forms/013_holiday_booth_request_form--event_planner_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
     <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Request A Holiday Booth</t>
+          <t>Event Title/Description</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -548,10 +548,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Select Event</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Event Type</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Select one option to indicate the type of event</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>no</t>
@@ -561,7 +565,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -571,7 +575,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Select Date</t>
+          <t>Event Space</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,7 +588,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -594,7 +598,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Select Time</t>
+          <t>Event Contact</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -617,7 +621,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Event Phone</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,7 +634,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -640,7 +644,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Booth Type</t>
+          <t>Event Email</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,7 +657,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -663,10 +667,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Select Booth Type</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Event Priority</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Select one option to indicate the event priority</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>no</t>
@@ -686,7 +694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Select Space</t>
+          <t>Event Category</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,7 +707,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -709,10 +717,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Select Space</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Event Status</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Select one option to indicate the event status</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>no</t>
@@ -722,7 +734,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -732,7 +744,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Select Contact</t>
+          <t>Event Location</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,7 +757,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -755,7 +767,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Select Phone</t>
+          <t>Event Team</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -778,7 +790,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Select Email</t>
+          <t>Event Notes</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,7 +803,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -801,7 +813,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Event Date</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -814,7 +826,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -824,264 +836,11 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Select Status</t>
+          <t>Event Time</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>event_planner_form_15</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Select Status</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>event_planner_form_16</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Select Priority</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>event_planner_form_17</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Select Priority</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>event_planner_form_18</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Select Category</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>event_planner_form_19</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Select Category</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>event_planner_form_20</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Select Location</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>event_planner_form_21</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Select Location</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>event_planner_form_22</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Select Team</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>event_planner_form_23</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Select Team</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>event_planner_form_24</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Select Event</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>event_planner_form_25</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
@@ -1131,12 +890,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1148,46 +907,46 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>event_planner_form_6_choices</t>
+          <t>event_planner_form_3_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>event_planner_form_6_choices</t>
+          <t>event_planner_form_3_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1199,12 +958,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1216,12 +975,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1233,12 +992,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1009,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1026,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1284,386 +1043,80 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>event_planner_form_14_choices</t>
+          <t>event_planner_form_10_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>event_planner_form_14_choices</t>
+          <t>event_planner_form_10_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>inactive</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Inactive</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>event_planner_form_15_choices</t>
+          <t>event_planner_form_11_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>event_planner_form_15_choices</t>
+          <t>event_planner_form_11_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>inactive</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Inactive</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>event_planner_form_16_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>event_planner_form_16_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>event_planner_form_17_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>event_planner_form_17_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>event_planner_form_18_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>event_planner_form_18_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>event_planner_form_19_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>event_planner_form_19_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>event_planner_form_20_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>event_planner_form_20_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>event_planner_form_21_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>event_planner_form_21_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>event_planner_form_22_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>event_planner_form_22_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>event_planner_form_23_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>event_planner_form_23_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>event_planner_form_24_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>event_planner_form_24_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
